--- a/第4回_Positional_Encoding/excel_positional_encoding_demo.xlsx
+++ b/第4回_Positional_Encoding/excel_positional_encoding_demo.xlsx
@@ -7167,7 +7167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A208"/>
+  <dimension ref="A1:H208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7204,9 +7204,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr"/>
-    </row>
+    <row r="6" ht="15" customHeight="1"/>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
@@ -7228,9 +7226,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr"/>
-    </row>
+    <row r="10" ht="15" customHeight="1"/>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
@@ -7252,9 +7248,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr"/>
-    </row>
+    <row r="14" ht="15" customHeight="1"/>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
@@ -7269,9 +7263,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr"/>
-    </row>
+    <row r="17" ht="15" customHeight="1"/>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
@@ -7293,9 +7285,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr"/>
-    </row>
+    <row r="21" ht="15" customHeight="1"/>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
@@ -7324,9 +7314,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr"/>
-    </row>
+    <row r="26" ht="15" customHeight="1"/>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
@@ -7348,9 +7336,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr"/>
-    </row>
+    <row r="30" ht="15" customHeight="1"/>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
@@ -7365,9 +7351,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr"/>
-    </row>
+    <row r="33" ht="15" customHeight="1"/>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
@@ -7431,9 +7415,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-    </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
@@ -7441,9 +7423,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-    </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
@@ -7486,9 +7466,7 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr"/>
-    </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
@@ -7545,9 +7523,7 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr"/>
-    </row>
+    <row r="61"/>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
@@ -7604,9 +7580,7 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr"/>
-    </row>
+    <row r="70"/>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
@@ -7677,9 +7651,7 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr"/>
-    </row>
+    <row r="81"/>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
@@ -7813,9 +7785,7 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr"/>
-    </row>
+    <row r="101"/>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
@@ -7865,9 +7835,7 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="inlineStr"/>
-    </row>
+    <row r="109"/>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
@@ -7896,9 +7864,7 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="inlineStr"/>
-    </row>
+    <row r="114"/>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
@@ -7990,9 +7956,7 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="inlineStr"/>
-    </row>
+    <row r="128"/>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
@@ -8014,9 +7978,7 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="inlineStr"/>
-    </row>
+    <row r="132"/>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
@@ -8031,9 +7993,7 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="inlineStr"/>
-    </row>
+    <row r="135"/>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
@@ -8041,9 +8001,7 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" t="inlineStr"/>
-    </row>
+    <row r="137"/>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
@@ -8100,9 +8058,7 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="inlineStr"/>
-    </row>
+    <row r="146"/>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
@@ -8159,9 +8115,7 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" t="inlineStr"/>
-    </row>
+    <row r="155"/>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
@@ -8218,9 +8172,7 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" t="inlineStr"/>
-    </row>
+    <row r="164"/>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
@@ -8284,9 +8236,7 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" t="inlineStr"/>
-    </row>
+    <row r="174"/>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
@@ -8343,9 +8293,7 @@
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" t="inlineStr"/>
-    </row>
+    <row r="183"/>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
@@ -8402,9 +8350,7 @@
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" t="inlineStr"/>
-    </row>
+    <row r="192"/>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
@@ -8461,9 +8407,7 @@
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" t="inlineStr"/>
-    </row>
+    <row r="201"/>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
@@ -8471,9 +8415,7 @@
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" t="inlineStr"/>
-    </row>
+    <row r="203"/>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
